--- a/artfynd/A 11943-2024 artfynd.xlsx
+++ b/artfynd/A 11943-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4167629</v>
+        <v>4214319</v>
       </c>
       <c r="B3" t="n">
-        <v>95510</v>
+        <v>95518</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221944</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -909,37 +909,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4214319</v>
+        <v>3001963</v>
       </c>
       <c r="B4" t="n">
-        <v>95518</v>
+        <v>96334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -955,7 +955,7 @@
         <v>6510881.61675199</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,6 +977,11 @@
           <t>Tanum</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>OB-Tan-1215</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
           <t>1998-08-30</t>
@@ -997,6 +1002,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>finns</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1005,35 +1015,34 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>barrskog, skogsväg</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Föreningen Bohusläns Flora</t>
+          <t>Bohuslän Floraväktarna</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Föreningen Bohusläns Flora</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Bohuslän Floraväktarna, Sven Bergqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3001963</v>
+        <v>90415786</v>
       </c>
       <c r="B5" t="n">
         <v>96334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1066,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>287090.668447374</v>
+        <v>287095.6360800355</v>
       </c>
       <c r="R5" t="n">
-        <v>6510881.61675199</v>
+        <v>6510886.553508282</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1094,11 +1103,6 @@
           <t>Tanum</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>OB-Tan-1215</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
           <t>1998-08-30</t>
@@ -1121,7 +1125,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>finns</t>
+          <t>Bohusläns flora - 2011.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,26 +1140,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bohuslän Floraväktarna</t>
+          <t>Evastina Blomgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bohuslän Floraväktarna, Sven Bergqvist</t>
+          <t>Sven Bergqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Bohusläns Flora 2011</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>90415786</v>
+        <v>90415785</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
+        <v>95717</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,25 +1168,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>220686</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1273,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>90415785</v>
+        <v>90415802</v>
       </c>
       <c r="B7" t="n">
-        <v>95717</v>
+        <v>95522</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1289,21 +1293,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220686</v>
+        <v>221946</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1343,7 +1347,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1998-08-30</t>
+          <t>1998-09-07</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1353,7 +1357,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1998-08-30</t>
+          <t>1998-09-07</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1383,7 +1387,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sven Bergqvist</t>
+          <t>Kjell Emanuelsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1394,10 +1398,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>90415802</v>
+        <v>90415763</v>
       </c>
       <c r="B8" t="n">
-        <v>95522</v>
+        <v>96254</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1410,23 +1414,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221946</v>
+        <v>223597</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1998-09-07</t>
+          <t>1999-05-30</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1998-09-07</t>
+          <t>1999-05-30</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kjell Emanuelsson</t>
+          <t>Sven Bergqvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1515,10 +1515,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>90415763</v>
+        <v>90415749</v>
       </c>
       <c r="B9" t="n">
-        <v>96254</v>
+        <v>95519</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1531,19 +1531,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223597</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1581,7 +1585,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1999-05-30</t>
+          <t>1998-08-30</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1591,7 +1595,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1999-05-30</t>
+          <t>1998-08-30</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1625,248 +1629,6 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr">
-        <is>
-          <t>Bohusläns Flora 2011</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>90415774</v>
-      </c>
-      <c r="B10" t="n">
-        <v>95511</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>221944</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Lopplummer</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Huperzia selago</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Litslebymoarna, SSV om Smedtorpet, Boh</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>287095.6360800355</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6510886.553508282</v>
-      </c>
-      <c r="S10" t="n">
-        <v>100</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Tanum</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Tanum</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>1998-08-30</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>1998-08-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Bohusläns flora - 2011.</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Evastina Blomgren</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Sven Bergqvist</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Bohusläns Flora 2011</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>90415749</v>
-      </c>
-      <c r="B11" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Litslebymoarna, SSV om Smedtorpet, Boh</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>287095.6360800355</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6510886.553508282</v>
-      </c>
-      <c r="S11" t="n">
-        <v>100</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Tanum</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Tanum</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>1998-08-30</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>1998-08-30</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Bohusläns flora - 2011.</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Evastina Blomgren</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Sven Bergqvist</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
         <is>
           <t>Bohusläns Flora 2011</t>
         </is>
